--- a/AAII_Financials/Yearly/CLLNY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CLLNY_YR_FIN.xlsx
@@ -1849,10 +1849,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>201000</v>
+        <v>58300</v>
       </c>
       <c r="E47" s="3">
-        <v>259200</v>
+        <v>133400</v>
       </c>
       <c r="F47" s="3">
         <v>261800</v>
@@ -2014,10 +2014,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>637200</v>
+        <v>779900</v>
       </c>
       <c r="E52" s="3">
-        <v>545900</v>
+        <v>671800</v>
       </c>
       <c r="F52" s="3">
         <v>349800</v>
